--- a/электробезопасность_V_ключи_тренажёр.xlsx
+++ b/электробезопасность_V_ключи_тренажёр.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Источник ключей</t>
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Бесплатный последовательный тренажёр prombez24.com/tests/212 (ЭБ 1260.25, V до и выше 1000 В). В HTML страниц /ticket/ordered ключ уже размечен полем correct=true.</t>
+          <t>1) prombez24.com/tests/212 — последовательные страницы /ticket/ordered, поле correct=true. 2) tests24.su — все 42 билета ЭБ 1260.25 сданы через WatuPRO (action=watupro_submit), ключ в классе correct-answer.</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Вопросов в тренажёре</t>
+          <t>Вопросов в тренажёре prombez24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -511,82 +511,104 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Совпало с РТН и проставлен ключ</t>
+          <t>Вопросов в билетах tests24.su</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Без ключа (нет в бесплатном банке)</t>
+          <t>Совпало с РТН и проставлен ключ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>281</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Точное совпадение формулировки</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>417</v>
+          <t>Разбивка по сайтам</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>prombez24: 13; prombez24 + tests24.su: 405; tests24.su: 2</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Совпадение без хвоста «согласно НПА»</t>
+          <t>Без ключа (нет в бесплатном банке)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Точное совпадение формулировки</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Совпадение без хвоста «согласно НПА»</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Нечёткое совпадение (опечатки РТН)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Нет пары</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Случайный тренажёр 10 вопросов (24тест.рф)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Не даёт полного покрытия: ~280 вопросов РТН в бесплатном последовательном банке нет. Повтор случайных билетов не «запоминает» недостающие.</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Нет пары</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Что даёт tests24 сверх prombez24</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Тот же курс ЭБ 1260.25, банк почти совпадает. Новые ключи к недостающим 281 вопросам РТН tests24 не добавляет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Память чата</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Ключи хранятся в этом файле, а не в контексте диалога.</t>
         </is>
@@ -603,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J421"/>
+  <dimension ref="A1:K421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -615,7 +637,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,6 +689,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Ссылка НПА в тренажёре</t>
         </is>
       </c>
@@ -711,6 +739,11 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>ч. 2 ст. 82 Федерального закона от 22.07.2008 N 123-ФЗ «Технический регламент о требованиях пожарной безопасности»</t>
         </is>
@@ -758,6 +791,11 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
           <t>ч. 3 ст. 82 Федерального закона от 22.07.2008 N 123-ФЗ «Технический регламент о требованиях пожарной безопасности»</t>
         </is>
       </c>
@@ -804,6 +842,11 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>ч. 4 ст. 82 Федерального закона от 22.07.2008 N 123-ФЗ «Технический регламент о требованиях пожарной безопасности»</t>
         </is>
       </c>
@@ -850,6 +893,11 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>ч. 12 ст. 82 Федерального закона от 22.07.2008 N 123-ФЗ "Технический регламент о требованиях пожарной безопасности"</t>
         </is>
       </c>
@@ -896,6 +944,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>п. 158 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -942,6 +995,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>п. 159 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -988,6 +1046,11 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>п. 159 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1034,6 +1097,11 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>п. 160 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1080,6 +1148,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>п. 161 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1126,6 +1199,11 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>п. 162 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1172,6 +1250,11 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>п. 366 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1218,6 +1301,11 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>п. 366 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1264,6 +1352,11 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>п. 366 Правил противопожарного режима в Российской Федерации, утв. Постановлением РФ от 16.09.2020г. N 1479</t>
         </is>
       </c>
@@ -1310,6 +1403,11 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1352,6 +1450,11 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>п. 57 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1398,6 +1501,11 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>п. 499 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1444,6 +1552,11 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>п. 526 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1490,6 +1603,11 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>п. 538 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1532,6 +1650,11 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>п. 604 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1578,6 +1701,11 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>п. 612 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1624,6 +1752,11 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>п. 613 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1652,11 +1785,11 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1670,9 +1803,10 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>п. 630 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
-        </is>
-      </c>
+          <t>tests24.su</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -1716,6 +1850,11 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>п. 633 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1762,6 +1901,11 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>п.  634 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1808,6 +1952,11 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>п. 637 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1854,6 +2003,11 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>п. 637 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1900,6 +2054,11 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1946,6 +2105,11 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -1992,6 +2156,11 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -2038,6 +2207,11 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -2084,6 +2258,11 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -2130,6 +2309,11 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -2176,6 +2360,11 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
           <t>Приложение №1 Правил технической эксплуатации электрических станций и сетей РФ, утв. приказом Минэнерго от 04.10.2022 РФ N 1070</t>
         </is>
       </c>
@@ -2218,6 +2407,11 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
           <t>п. 10 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2260,6 +2454,11 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
           <t>п. 11 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2302,6 +2501,11 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
           <t>п. 18 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2344,6 +2548,11 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>п. 61 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2386,6 +2595,11 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
           <t>п. 61 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2428,6 +2642,11 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
           <t>п. 61 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2470,6 +2689,11 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
           <t>п. 61 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2512,6 +2736,11 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
           <t>п. 63 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2554,6 +2783,11 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
           <t>п. 64 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2596,6 +2830,11 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
           <t>п. 64 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2638,6 +2877,11 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
           <t>п. 64 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2680,6 +2924,11 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
           <t>п. 64 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2722,6 +2971,11 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
           <t>п. 65, 69 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2764,6 +3018,11 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>п. 69 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2806,6 +3065,11 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
           <t>п. 76 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2848,6 +3112,11 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
           <t>п. 79 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2890,6 +3159,11 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
           <t>п. 81 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2932,6 +3206,11 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
           <t>п. 83 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -2974,6 +3253,11 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
           <t>п. 94 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3016,6 +3300,11 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
           <t>п. 94 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3058,6 +3347,11 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
           <t>п. 95 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3100,6 +3394,11 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
           <t>п. 95 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3142,6 +3441,11 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
           <t>п. 96, 69 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3184,6 +3488,11 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
           <t>п. 101 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3226,6 +3535,11 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
           <t>п. 103 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3268,6 +3582,11 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
           <t>п. 104 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3310,6 +3629,11 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
           <t>п. 105 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3352,6 +3676,11 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
           <t>п. 107 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3394,6 +3723,11 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
           <t>п. 111 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3435,6 +3769,11 @@
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>п. 112 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
@@ -3481,6 +3820,11 @@
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>п. 113 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
@@ -3529,6 +3873,11 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
           <t>п. 114 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3571,6 +3920,11 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
           <t>п. 115 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3613,6 +3967,11 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
           <t>п. 115 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3655,6 +4014,11 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
           <t>п. 122 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3697,6 +4061,11 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
           <t>п. 123 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3739,6 +4108,11 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
           <t>п. 124 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3781,6 +4155,11 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
           <t>п. 125 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3823,6 +4202,11 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
           <t>п. 127 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3865,6 +4249,11 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
           <t>п. 136 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3907,6 +4296,11 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
           <t>п. 139 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3949,6 +4343,11 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
           <t>п. 147 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -3991,6 +4390,11 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
           <t>п. 154 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4033,6 +4437,11 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
           <t>п. 177 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4075,6 +4484,11 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
           <t>п. 181 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4117,6 +4531,11 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
           <t>п. 183 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4159,6 +4578,11 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
           <t>п. 185 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4201,6 +4625,11 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
           <t>п. 196 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4243,6 +4672,11 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
           <t>п. 201 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4285,6 +4719,11 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
           <t>п. 211 Правил переключений в электроустановках, утв. приказом Минэнерго РФ от 13.09.2018 N 757</t>
         </is>
       </c>
@@ -4331,6 +4770,11 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4377,6 +4821,11 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4423,6 +4872,11 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4469,6 +4923,11 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
           <t>п. 2.11 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4515,6 +4974,11 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4561,6 +5025,11 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4607,6 +5076,11 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4653,6 +5127,11 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4699,6 +5178,11 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
           <t>п. 2.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4745,6 +5229,11 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
           <t>п. 2.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4791,6 +5280,11 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
           <t>п. 3.10 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4833,6 +5327,11 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
           <t>п. 3.11 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4879,6 +5378,11 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
           <t>п. 3.13 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4925,6 +5429,11 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
           <t>п. 3.13 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -4971,6 +5480,11 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
           <t>п. 3.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5017,6 +5531,11 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
           <t>п. 3.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5059,6 +5578,11 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
           <t>п. 3.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Министерства труда и соц. Защиты РФ №903н от 15.12.2020</t>
         </is>
       </c>
@@ -5101,6 +5625,11 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
           <t>п. 3.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5143,6 +5672,11 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
           <t>п. 3.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5189,6 +5723,11 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
           <t>п. 3.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5235,6 +5774,11 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
           <t>п. 3.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5281,6 +5825,11 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
           <t>п. 3.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5327,6 +5876,11 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
           <t>п. 3.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5373,6 +5927,11 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
           <t>п. 3.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5415,6 +5974,11 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
           <t>п. 3.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5461,6 +6025,11 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
           <t>п. 3.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5507,6 +6076,11 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
           <t>п. 3.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5549,6 +6123,11 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
           <t>п. 3.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5595,6 +6174,11 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
           <t>п. 4.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5641,6 +6225,11 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
           <t>п. 4.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5687,6 +6276,11 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
           <t>п. 4.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5733,6 +6327,11 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
           <t>п. 4.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5779,6 +6378,11 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
           <t>п. 5.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5825,6 +6429,11 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
           <t>п. 5.10 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5871,6 +6480,11 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
           <t>п. 5.13 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5917,6 +6531,11 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
           <t>п. 5.13 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -5963,6 +6582,11 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
           <t>п. 5.15 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6009,6 +6633,11 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
           <t>п. 5.16 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6055,6 +6684,11 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
           <t>п. 5.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6101,6 +6735,11 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
           <t>п. 5.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6147,6 +6786,11 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
           <t>п. 5.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6193,6 +6837,11 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
           <t>п. 5.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6239,6 +6888,11 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
           <t>п. 5.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6285,6 +6939,11 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
           <t>п. 5.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6331,6 +6990,11 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
           <t>п. 5.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6373,6 +7037,11 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
           <t>п. 5.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6419,6 +7088,11 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
           <t>п. 5.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6461,6 +7135,11 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
           <t>п. 5.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6507,6 +7186,11 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
           <t>п. 5.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6553,6 +7237,11 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6599,6 +7288,11 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
           <t>п. 6.12 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6645,6 +7339,11 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
           <t>п. 6.13 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6691,6 +7390,11 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
           <t>п. 6.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6737,6 +7441,11 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
           <t>п. 6.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6783,6 +7492,11 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
           <t>п. 6.32 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6829,6 +7543,11 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
           <t>п. 6.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6875,6 +7594,11 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
           <t>п. 6.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6921,6 +7645,11 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
           <t>п. 6.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -6967,6 +7696,11 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
           <t>п. 6.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7013,6 +7747,11 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
           <t>п. 6.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7059,6 +7798,11 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
           <t>п. 6.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7105,6 +7849,11 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
           <t>п. 6.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7151,6 +7900,11 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
           <t>п. 6.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7197,6 +7951,11 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
           <t>п. 6.9 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7243,6 +8002,11 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
           <t>п. 7.10 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7289,6 +8053,11 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
           <t>п. 8.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7335,6 +8104,11 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
           <t>п. 8.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7381,6 +8155,11 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
           <t>п. 8.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7427,6 +8206,11 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
           <t>п. 10.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7473,6 +8257,11 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
           <t>п. 10.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7519,6 +8308,11 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
           <t>п. 10.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7565,6 +8359,11 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
           <t>п. 10.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7611,6 +8410,11 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
           <t>п. 10.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7657,6 +8461,11 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
           <t>п. 10.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7703,6 +8512,11 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
           <t>п. 10.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7749,6 +8563,11 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
           <t>п. 10.8 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7795,6 +8614,11 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
           <t>п. 18.1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7841,6 +8665,11 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
           <t>п. 35.12 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7887,6 +8716,11 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
           <t>п. 38.14 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7933,6 +8767,11 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
           <t>п. 38.21 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -7979,6 +8818,11 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
           <t>п. 38.21 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8025,6 +8869,11 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
           <t>п. 38.23 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8071,6 +8920,11 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
           <t>п. 38.37 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8117,6 +8971,11 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
           <t>п. 38.65 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8163,6 +9022,11 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
           <t>п. 38.81 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8209,6 +9073,11 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
           <t>п. 44.3 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8255,6 +9124,11 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
           <t>п. 44.9, 44.5 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8301,6 +9175,11 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
           <t>п. 46.2 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8347,6 +9226,11 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
           <t>п. 46.4 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8393,6 +9277,11 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
           <t>п. 46.6 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8439,6 +9328,11 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
           <t>п. 47.6-47.7 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8485,6 +9379,11 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
           <t>Прил. N 1 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -8531,6 +9430,11 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
           <t>п. 3 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8577,6 +9481,11 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
           <t>п. 6 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8623,6 +9532,11 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
           <t>п. 7 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8669,6 +9583,11 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
           <t>п. 10 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8715,6 +9634,11 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
           <t>п. 10 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8761,6 +9685,11 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
           <t>п. 13 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8807,6 +9736,11 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
           <t>п. 10 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8853,6 +9787,11 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
           <t>п. 19 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8899,6 +9838,11 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
           <t>п. 21 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8945,6 +9889,11 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
           <t>п. 24 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -8991,6 +9940,11 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
           <t>п. 25 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9037,6 +9991,11 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
           <t>п. 28 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9083,6 +10042,11 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9129,6 +10093,11 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
           <t>п. 30 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9175,6 +10144,11 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9221,6 +10195,11 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9267,6 +10246,11 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
           <t>п. 36 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9313,6 +10297,11 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
           <t>п. 38 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9359,6 +10348,11 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
           <t>п. 41 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9405,6 +10399,11 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
           <t>п. 42 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9451,6 +10450,11 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9497,6 +10501,11 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
           <t>п. 44 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9543,6 +10552,11 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
           <t>п. 45 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9589,6 +10603,11 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
           <t>п. 46 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9635,6 +10654,11 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
           <t>п. 47 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9681,6 +10705,11 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
           <t>п. 54 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9727,6 +10756,11 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
           <t>п. 57 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9773,6 +10807,11 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
           <t>п. 59 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9819,6 +10858,11 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
           <t>п. 60 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9865,6 +10909,11 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
           <t>п. 61 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9911,6 +10960,11 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
           <t>п. 63 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -9957,6 +11011,11 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
           <t>п. 66 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10003,6 +11062,11 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
           <t>п. 67 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10049,6 +11113,11 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
           <t>п. 68 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10095,6 +11164,11 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
           <t>п. 69 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10141,6 +11215,11 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
           <t>п. 73 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10187,6 +11266,11 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
           <t>п. 76 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10233,6 +11317,11 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
           <t>п. 77 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10279,6 +11368,11 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
           <t>п. 79 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10325,6 +11419,11 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
           <t>п. 80 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10371,6 +11470,11 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
           <t>п. 84 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10417,6 +11521,11 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
           <t>п. 85 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10463,6 +11572,11 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
           <t>п. 87 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10509,6 +11623,11 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
           <t>п. 88 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10555,6 +11674,11 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
           <t>п. 92 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10601,6 +11725,11 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
           <t>п. 95 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10647,6 +11776,11 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
           <t>п. 97 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10693,6 +11827,11 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
           <t>п. 98 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10739,6 +11878,11 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
           <t>п. 106 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10785,6 +11929,11 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
           <t>п. 109 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
         </is>
       </c>
@@ -10827,6 +11976,11 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
           <t>п. 3 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -10873,6 +12027,11 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
           <t>п. 7 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -10915,6 +12074,11 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
           <t>п. 7 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -10961,6 +12125,11 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
           <t>п. 8 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11007,6 +12176,11 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
           <t>п. 8 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11049,6 +12223,11 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
           <t>п. 8 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11091,6 +12270,11 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
           <t>п. 9 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11137,6 +12321,11 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
           <t>п. 9 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11183,6 +12372,11 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
           <t>п. 9 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11225,6 +12419,11 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
           <t>п. 9 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11271,6 +12470,11 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
           <t>п. 9 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11313,6 +12517,11 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
           <t>п. 10 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11355,6 +12564,11 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
           <t>п. 11 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11397,6 +12611,11 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
           <t>п. 17 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11439,6 +12658,11 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
           <t>п. 19 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11481,6 +12705,11 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
           <t>п. 20 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11523,6 +12752,11 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
           <t>п. 23 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11565,6 +12799,11 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
           <t>п. 23 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11611,6 +12850,11 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
           <t>п. 23 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11657,6 +12901,11 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
           <t>п. 25 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11699,6 +12948,11 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11741,6 +12995,11 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11783,6 +13042,11 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11825,6 +13089,11 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11867,6 +13136,11 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11909,6 +13183,11 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11951,6 +13230,11 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -11993,6 +13277,11 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12035,6 +13324,11 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12077,6 +13371,11 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12119,6 +13418,11 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12161,6 +13465,11 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12203,6 +13512,11 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
           <t>п. 26 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12249,6 +13563,11 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
           <t>п. 27 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12295,6 +13614,11 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
           <t>п. 27 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12341,6 +13665,11 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
           <t>п. 27 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12383,6 +13712,11 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
           <t>п. 27 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12429,6 +13763,11 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12475,6 +13814,11 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12521,6 +13865,11 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12567,6 +13916,11 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12613,6 +13967,11 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
           <t>п. 29 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12659,6 +14018,11 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
           <t>п. 30 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12701,6 +14065,11 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
           <t>п. 30 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12743,6 +14112,11 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
           <t>п. 30 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12789,6 +14163,11 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
           <t>п. 31 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12835,6 +14214,11 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
           <t>п. 31, 33 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12877,6 +14261,11 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
           <t>п. 31 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12919,6 +14308,11 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -12961,6 +14355,11 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13007,6 +14406,11 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13049,6 +14453,11 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
           <t>п. 33 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13091,6 +14500,11 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
           <t>п. 34 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13137,6 +14551,11 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
           <t>п. 37 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13183,6 +14602,11 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
           <t>п. 38 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13229,6 +14653,11 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
           <t>п. 38 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13271,6 +14700,11 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
           <t>п. 39 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13317,6 +14751,11 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
           <t>п. 40 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13363,6 +14802,11 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
           <t>п. 40 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13405,6 +14849,11 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
           <t>п. 40 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13447,6 +14896,11 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
           <t>п. 41 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13489,6 +14943,11 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
           <t>п. 41 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13531,6 +14990,11 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
           <t>п. 41 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13577,6 +15041,11 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
           <t>п. 42 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13623,6 +15092,11 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13669,6 +15143,11 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13715,6 +15194,11 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13757,6 +15241,11 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13803,6 +15292,11 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
           <t>п. 43 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13845,6 +15339,11 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
           <t>п. 44 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13891,6 +15390,11 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
           <t>п. 45 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13937,6 +15441,11 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
           <t>п. 48 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -13983,6 +15492,11 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
           <t>п. 57 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -14029,6 +15543,11 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -14075,6 +15594,11 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 №811</t>
         </is>
       </c>
@@ -14121,6 +15645,11 @@
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 №811</t>
         </is>
       </c>
@@ -14167,6 +15696,11 @@
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 №811</t>
         </is>
       </c>
@@ -14209,6 +15743,11 @@
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 №811</t>
         </is>
       </c>
@@ -14251,6 +15790,11 @@
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 №811</t>
         </is>
       </c>
@@ -14297,6 +15841,11 @@
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
           <t>Приложение N1 Правил технической эксплуатации электроустановок потребителей электрической энергии, утв. приказом Минэнерго РФ от 12.08.2022 N 811</t>
         </is>
       </c>
@@ -14343,6 +15892,11 @@
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.6 - 1.1.10 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14389,6 +15943,11 @@
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.6 - 1.1.10 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14435,6 +15994,11 @@
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.6 - 1.1.10 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14481,6 +16045,11 @@
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.13 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14527,6 +16096,11 @@
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.29 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14573,6 +16147,11 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.28, 1.1.29 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14619,6 +16198,11 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.30 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14665,6 +16249,11 @@
       </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.30 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14711,6 +16300,11 @@
       </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
           <t>п. 1.1.30 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14757,6 +16351,11 @@
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.7 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14803,6 +16402,11 @@
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.8 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14849,6 +16453,11 @@
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.9 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14895,6 +16504,11 @@
       </c>
       <c r="J319" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.10 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14937,6 +16551,11 @@
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.11 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -14979,6 +16598,11 @@
       </c>
       <c r="J321" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.11 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15021,6 +16645,11 @@
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.16 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15063,6 +16692,11 @@
       </c>
       <c r="J323" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.16 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15109,6 +16743,11 @@
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.17 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15155,6 +16794,11 @@
       </c>
       <c r="J325" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.18 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15201,6 +16845,11 @@
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.19 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15247,6 +16896,11 @@
       </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
           <t>п. 1.2.21 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15293,6 +16947,11 @@
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.3 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15339,6 +16998,11 @@
       </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.3 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15385,6 +17049,11 @@
       </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.3 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15431,6 +17100,11 @@
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.5 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15477,6 +17151,11 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.13 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15523,6 +17202,11 @@
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.14 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15569,6 +17253,11 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.15 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15615,6 +17304,11 @@
       </c>
       <c r="J335" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.16 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15661,6 +17355,11 @@
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.17 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15707,6 +17406,11 @@
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.28 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15753,6 +17457,11 @@
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.29 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15799,6 +17508,11 @@
       </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.39 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15845,6 +17559,11 @@
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.41 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15891,6 +17610,11 @@
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.42 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15937,6 +17661,11 @@
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.47 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -15983,6 +17712,11 @@
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.90 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16025,6 +17759,11 @@
       </c>
       <c r="J344" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.98 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16071,6 +17810,11 @@
       </c>
       <c r="J345" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.101 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16117,6 +17861,11 @@
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.107 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16163,6 +17912,11 @@
       </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.109 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16209,6 +17963,11 @@
       </c>
       <c r="J348" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.117 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16255,6 +18014,11 @@
       </c>
       <c r="J349" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.117 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16301,6 +18065,11 @@
       </c>
       <c r="J350" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.121 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16347,6 +18116,11 @@
       </c>
       <c r="J351" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.121 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16393,6 +18167,11 @@
       </c>
       <c r="J352" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.123 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16439,6 +18218,11 @@
       </c>
       <c r="J353" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.127 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16485,6 +18269,11 @@
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.127 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16513,11 +18302,11 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G355" s="2" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -16531,9 +18320,10 @@
       </c>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>п. 1.7.127 Правил устройства электроустановок</t>
-        </is>
-      </c>
+          <t>tests24.su</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr"/>
     </row>
     <row r="356" ht="48" customHeight="1">
       <c r="A356" s="2" t="n">
@@ -16577,6 +18367,11 @@
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.137 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16623,6 +18418,11 @@
       </c>
       <c r="J357" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.137 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16669,6 +18469,11 @@
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.137 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16715,6 +18520,11 @@
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.142 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16761,6 +18571,11 @@
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
           <t>п. 1.7.148, 1.7.149 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16803,6 +18618,11 @@
       </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
           <t>п. 1.9.13 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16849,6 +18669,11 @@
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
           <t>п. 2.1.15 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16895,6 +18720,11 @@
       </c>
       <c r="J363" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
           <t>п. 2.1.19 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16941,6 +18771,11 @@
       </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
           <t>п. 2.1.51 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -16987,6 +18822,11 @@
       </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
           <t>п. 2.1.51 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17033,6 +18873,11 @@
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.23 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17075,6 +18920,11 @@
       <c r="I367" s="2" t="inlineStr"/>
       <c r="J367" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.25 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17121,6 +18971,11 @@
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.25 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17167,6 +19022,11 @@
       </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.25 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17213,6 +19073,11 @@
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.25 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17255,6 +19120,11 @@
       <c r="I371" s="2" t="inlineStr"/>
       <c r="J371" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.85 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17297,6 +19167,11 @@
       <c r="I372" s="2" t="inlineStr"/>
       <c r="J372" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.89 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17343,6 +19218,11 @@
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.108 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17389,6 +19269,11 @@
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.115 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17435,6 +19320,11 @@
       </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.134 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17481,6 +19371,11 @@
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
           <t>п. 2.3.134 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17527,6 +19422,11 @@
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
           <t>п. 2.4.50 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17573,6 +19473,11 @@
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
           <t>п. 2.4.50 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17619,6 +19524,11 @@
       </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.3 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17665,6 +19575,11 @@
       </c>
       <c r="J380" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.4 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17711,6 +19626,11 @@
       </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.5 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17757,6 +19677,11 @@
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.8 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17799,6 +19724,11 @@
       <c r="I383" s="2" t="inlineStr"/>
       <c r="J383" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.12 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17845,6 +19775,11 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.14 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17891,6 +19826,11 @@
       </c>
       <c r="J385" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.14 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17937,6 +19877,11 @@
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.17 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -17983,6 +19928,11 @@
       </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.21 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18029,6 +19979,11 @@
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
           <t>п. 6.1.21 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18071,6 +20026,11 @@
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="inlineStr">
+        <is>
           <t>п. 6.2.2 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18117,6 +20077,11 @@
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
           <t>п. 6.2.7 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18159,6 +20124,11 @@
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
           <t>п. 6.5.22 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18205,6 +20175,11 @@
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
           <t>п. 6.6.2 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18251,6 +20226,11 @@
       </c>
       <c r="J393" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr">
+        <is>
           <t>п. 6.6.21, 6.6.30 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18297,6 +20277,11 @@
       </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
           <t>п. 7.1.15 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18343,6 +20328,11 @@
       </c>
       <c r="J395" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr">
+        <is>
           <t>п. 7.1.28 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18389,6 +20379,11 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
           <t>п. 7.1.45 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18431,6 +20426,11 @@
       <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
+          <t>prombez24</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
           <t>п. 7.1.49 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18477,6 +20477,11 @@
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.19 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18523,6 +20528,11 @@
       </c>
       <c r="J399" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.24 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18569,6 +20579,11 @@
       </c>
       <c r="J400" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
           <t>п.7.6.25 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18615,6 +20630,11 @@
       </c>
       <c r="J401" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.27 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18661,6 +20681,11 @@
       </c>
       <c r="J402" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.35 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18707,6 +20732,11 @@
       </c>
       <c r="J403" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.37 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18753,6 +20783,11 @@
       </c>
       <c r="J404" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.57 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18799,6 +20834,11 @@
       </c>
       <c r="J405" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.57 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18845,6 +20885,11 @@
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
           <t>п. 7.6.57 Правил устройства электроустановок</t>
         </is>
       </c>
@@ -18891,6 +20936,11 @@
       </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
           <t>п. 3-4 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -18937,6 +20987,11 @@
       </c>
       <c r="J408" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
           <t>п. 5 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -18983,6 +21038,11 @@
       </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr">
+        <is>
           <t>п. 5 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19029,6 +21089,11 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
           <t>п. 8 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19074,6 +21139,11 @@
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr">
         <is>
           <t>п. 9-10 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
@@ -19130,6 +21200,11 @@
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19184,6 +21259,11 @@
       </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19233,6 +21313,11 @@
       </c>
       <c r="J414" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19281,6 +21366,11 @@
       </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19328,6 +21418,11 @@
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
         <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
@@ -19381,6 +21476,11 @@
       </c>
       <c r="J417" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19427,6 +21527,11 @@
       </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19473,6 +21578,11 @@
       </c>
       <c r="J419" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
           <t>Приложение N 2 Порядка оказания первой помощи, утв. приказом Минздрава России от 03.05.2024 N 220н</t>
         </is>
       </c>
@@ -19515,6 +21625,11 @@
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
           <t>п. 38.65 Правил по охране труда при эксплуатации электроустановок, утв. приказом Минтруда РФ от 15.12.2020 N 903н</t>
         </is>
       </c>
@@ -19560,6 +21675,11 @@
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>prombez24 + tests24.su</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="inlineStr">
         <is>
           <t>п. 7.6.35 Правил устройства электроустановок</t>
         </is>
@@ -24600,7 +26720,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.425</v>
+        <v>0.474</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>

--- a/электробезопасность_V_ключи_тренажёр.xlsx
+++ b/электробезопасность_V_ключи_тренажёр.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ключи" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Без ключа" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ключи_развёрнуто" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ключи" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без ключа" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ключи_развёрнуто" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>prombez24: 13; prombez24 + tests24.su: 405; tests24.su: 2</t>
+          <t>24тест V выше 1000 + 24тест IV до 1000: 1; prombez24 + 24тест IV до 1000: 7; prombez24 + 24тест V выше 1000: 2; prombez24 + 24тест V выше 1000 + 24тест IV до 1000: 4; prombez24 + tests24.su + 24тест V выше 1000: 106; prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000: 298; tests24.su: 1; tests24.su + 24тест V выше 1000 + 24тест IV до 1000: 1</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -740,7 +740,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -11095,11 +11095,11 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -11113,12 +11113,12 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>п. 68 Правил работы с персоналом в организациях электроэнергетики РФ, утв. приказом Минэнерго РФ от 22.09.2020 N 796</t>
+          <t>Правила работы с персоналом в организациях электроэнергетики Российской Федерации (Приказ Минэнерго № 796 от 22.09.2020)68. Допуск к дублированию при подготовке по новой должности должен быть оформлен организационно-распорядительным документом организации (ее филиала, представительства), содержащим сроки дублирования, указание лиц, ответственных за дублирование работника, допущенного к дублированию, предоставленные работнику, допущенному к дублированию, права (ведения оперативных переговоров, переключений) на период дублирования.Допуск к дублированию после перерыва в работе более 30 календарных дней должен быть оформлен в порядке, определенном организацией.О допуске к дублированию при подготовке по новой должности диспетчерского, оперативного и оперативно-ремонтного персонала должны быть уведомлены соответствующий персонал своей организации, а также персонал субъектов электроэнергетики и потребителей электрической энергии, с работниками которых осуществляется технологическое взаимодействие.За действия работника, допущенного к дублированию на рабочем месте, несут ответственность, предусмотренную законодательством Российской Федерации, в равной мере как сам работник, допущенный к дублированию, так и работник, под руководством и контролем которого проводится дублирование.</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11164,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K313" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K315" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K318" s="2" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="J319" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K320" s="2" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="J321" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K321" s="2" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K322" s="2" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K327" s="2" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr">
@@ -17457,7 +17457,7 @@
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K338" s="2" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K341" s="2" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K342" s="2" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K343" s="2" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="J344" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K344" s="2" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="J345" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K345" s="2" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K346" s="2" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K347" s="2" t="inlineStr">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="J348" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="J349" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K349" s="2" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K350" s="2" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -18218,7 +18218,7 @@
       </c>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K354" s="2" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>tests24.su</t>
+          <t>tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr"/>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="J357" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K357" s="2" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K362" s="2" t="inlineStr">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="J363" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K363" s="2" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K364" s="2" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K365" s="2" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K366" s="2" t="inlineStr">
@@ -18920,7 +18920,7 @@
       <c r="I367" s="2" t="inlineStr"/>
       <c r="J367" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K367" s="2" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K368" s="2" t="inlineStr">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K369" s="2" t="inlineStr">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr">
@@ -19120,7 +19120,7 @@
       <c r="I371" s="2" t="inlineStr"/>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K371" s="2" t="inlineStr">
@@ -19167,7 +19167,7 @@
       <c r="I372" s="2" t="inlineStr"/>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K372" s="2" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K373" s="2" t="inlineStr">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K374" s="2" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K375" s="2" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K376" s="2" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K378" s="2" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K379" s="2" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K380" s="2" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K381" s="2" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K382" s="2" t="inlineStr">
@@ -19724,7 +19724,7 @@
       <c r="I383" s="2" t="inlineStr"/>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K383" s="2" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K384" s="2" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K385" s="2" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K386" s="2" t="inlineStr">
@@ -19928,7 +19928,7 @@
       </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K387" s="2" t="inlineStr">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -20026,7 +20026,7 @@
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K389" s="2" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -20124,7 +20124,7 @@
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K391" s="2" t="inlineStr">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K394" s="2" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K395" s="2" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K396" s="2" t="inlineStr">
@@ -20426,7 +20426,7 @@
       <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>prombez24</t>
+          <t>prombez24 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K397" s="2" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K398" s="2" t="inlineStr">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K399" s="2" t="inlineStr">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K400" s="2" t="inlineStr">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K401" s="2" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K402" s="2" t="inlineStr">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K403" s="2" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K405" s="2" t="inlineStr">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K406" s="2" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K407" s="2" t="inlineStr">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K408" s="2" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K409" s="2" t="inlineStr">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K410" s="2" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K411" s="2" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K412" s="2" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K413" s="2" t="inlineStr">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K414" s="2" t="inlineStr">
@@ -21366,7 +21366,7 @@
       </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K415" s="2" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K416" s="2" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K417" s="2" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K418" s="2" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K419" s="2" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K420" s="2" t="inlineStr">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>prombez24 + tests24.su</t>
+          <t>prombez24 + tests24.su + 24тест V выше 1000 + 24тест IV до 1000</t>
         </is>
       </c>
       <c r="K421" s="2" t="inlineStr">
